--- a/Cloud Connect/CloudConnect_Daily_Task_Plan.xlsx
+++ b/Cloud Connect/CloudConnect_Daily_Task_Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhans\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhans\Desktop\sem5-project\Cloud Connect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A0BFD4-5564-44A9-9AC6-BA648F9AC904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFFC646-BCF8-4599-8811-8D79D74CFD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="86">
   <si>
     <t>Day</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -657,7 +660,7 @@
     <col min="1" max="1" width="8.88671875" style="2"/>
     <col min="2" max="2" width="26" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -672,7 +675,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -685,6 +688,9 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
@@ -696,6 +702,9 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
@@ -707,6 +716,9 @@
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -717,6 +729,9 @@
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
